--- a/output/pdf_financials_xlsx/SPSA.P.xlsx
+++ b/output/pdf_financials_xlsx/SPSA.P.xlsx
@@ -1228,19 +1228,19 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>1e-06</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.19738</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.449148</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.412754</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.379982</v>
       </c>
     </row>
     <row r="35">
@@ -1272,19 +1272,19 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>1e-06</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.19738</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.449148</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.412754</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.379982</v>
       </c>
     </row>
     <row r="37">
@@ -3825,7 +3825,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -4992,11 +4992,7 @@
           <t>General and administrative fees</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
+      <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
           <t>-</t>
